--- a/auxiliary-data/slurry properties.xlsx
+++ b/auxiliary-data/slurry properties.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{DADC88A7-B2D0-45B5-8022-27858212C112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{286E5C2A-7A1C-4C10-91E8-130F9F4CACAB}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{DADC88A7-B2D0-45B5-8022-27858212C112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02BDC0B-741F-40C9-840A-D2FB037D6219}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -185,60 +185,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -275,47 +227,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,6 +598,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1" t="s">
         <v>25</v>
@@ -701,16 +644,16 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -749,1830 +692,1971 @@
       <c r="P2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>44656</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>8.0399999999999991</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>22.411003236245953</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>88.119461765671147</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>3.7644448727833462</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>0.34424830261881667</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="10">
         <v>67.87</v>
       </c>
-      <c r="K3" s="11">
-        <v>0</v>
-      </c>
-      <c r="L3" s="11">
-        <v>0</v>
-      </c>
-      <c r="M3" s="11">
-        <v>0</v>
-      </c>
-      <c r="N3" s="11">
-        <v>0</v>
-      </c>
-      <c r="O3" s="11">
-        <v>0</v>
-      </c>
-      <c r="P3" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>0</v>
-      </c>
-      <c r="R3" s="11">
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
         <v>67.87</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>44656</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>8.01</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>22.578430699526326</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>87.899057464274904</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>3.3459445350734089</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>0.5224352517985611</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <v>62.95</v>
       </c>
-      <c r="K4" s="11">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11">
-        <v>0</v>
-      </c>
-      <c r="M4" s="11">
-        <v>0</v>
-      </c>
-      <c r="N4" s="11">
-        <v>0</v>
-      </c>
-      <c r="O4" s="11">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>0</v>
-      </c>
-      <c r="R4" s="11">
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0</v>
+      </c>
+      <c r="P4" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>0</v>
+      </c>
+      <c r="R4" s="10">
         <v>62.95</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>44656</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>7.53</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>4.1734396854799076</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>70.380434782608688</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>2.4835909090909092</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>1.1950286806883363</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>1152.3800000000001</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>668.77</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>59.14</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>49.71</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>78.86</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>19.170000000000002</v>
       </c>
-      <c r="P5" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
         <v>9.14</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="10">
         <v>2037.1700000000003</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>44656</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>7.53</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>4.1509314875398422</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>69.944247339077506</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>2.4807328190743339</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>1.0638297872340428</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <v>1169.94</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>677.96</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>57.87</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>48.89</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>81.7</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <v>14.29</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="10">
         <v>13.83</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="10">
         <v>12.36</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="10">
         <v>2076.84</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>44656</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>7.53</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>6.2608628008801359</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>77.209393137968377</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>2.7338771593090208</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>1.1482254697286014</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <v>1441.58</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <v>552.22</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <v>70.39</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <v>44.82</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <v>87.25</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <v>10.84</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="10">
         <v>17.14</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="10">
         <v>19.63</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="10">
         <v>2243.8700000000003</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>44656</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>7.48</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>6.1342631396609342</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>76.571324467116042</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>2.7004040219378429</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>1.1026293469041559</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <v>1464.54</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <v>569.65</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="10">
         <v>71.58</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="10">
         <v>45.89</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <v>90.97</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <v>21.29</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="10">
         <v>8.61</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="10">
         <v>45</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="10">
         <v>2317.5299999999997</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="4">
         <v>44663</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>21.882001493651977</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>92.984452028820641</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>2.7725159651669085</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>0.68817267927848658</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>67.36</v>
       </c>
-      <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
         <v>67.36</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="4">
         <v>44663</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>8.34</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>22.708688245315166</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>92.610652663165794</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>2.6880632530120483</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>0.73645392100744134</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <v>65.44</v>
       </c>
-      <c r="K10" s="11">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11">
-        <v>0</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11">
+      <c r="K10" s="10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
         <v>65.44</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="4">
         <v>44663</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>7.36</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>2.3776109278881008</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>69.749139203148033</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>1.5911916201117318</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>1.0464058234758873</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <v>2422.5</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="10">
         <v>1213.33</v>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="10">
         <v>301.77</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <v>790.29</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <v>394.96</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="10">
         <v>213.51</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="10">
         <v>9.0399999999999991</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="10">
         <v>74.13</v>
       </c>
-      <c r="R11" s="11">
+      <c r="R11" s="10">
         <v>5419.53</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="4">
         <v>44663</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>7.36</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>2.3919763150000648</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>69.792802617230123</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>2.2167138157894737</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>0.97297297297297292</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <v>2428.4499999999998</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>1209.24</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="10">
         <v>299.05</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <v>789.73</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <v>397.32</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="10">
         <v>216.27</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="10">
         <v>8.7899999999999991</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="10">
         <v>147.07</v>
       </c>
-      <c r="R12" s="11">
+      <c r="R12" s="10">
         <v>5495.9199999999992</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>4</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="4">
         <v>44663</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>7.16</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>3.5833111878820092</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>76.980124592109149</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>2.0558703256936068</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>1.1413043478260869</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <v>3089.68</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <v>1560.17</v>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="10">
         <v>304.77</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <v>976.86</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="10">
         <v>396.89</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="10">
         <v>239.92</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="10">
         <v>9.8800000000000008</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="10">
         <v>160.63</v>
       </c>
-      <c r="R13" s="11">
+      <c r="R13" s="10">
         <v>6738.8000000000011</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="4">
         <v>44663</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>7.16</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>3.682926245783595</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>77.52517050990582</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>1.999936991869919</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>1.1879049676025919</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <v>3085.25</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <v>1558.56</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="10">
         <v>304.32</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="10">
         <v>975.25</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="10">
         <v>392.35</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="10">
         <v>238.2</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="10">
         <v>9.44</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="10">
         <v>151.44999999999999</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="10">
         <v>6714.8199999999988</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="4">
         <v>44670</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>8</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>21.69265391416171</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="8">
+      <c r="G15" s="8"/>
+      <c r="H15" s="7">
         <v>4.1806156015037592</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>0.33090072057646119</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <v>66.59</v>
       </c>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11">
-        <v>0</v>
-      </c>
-      <c r="P15" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>0</v>
-      </c>
-      <c r="R15" s="11">
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0</v>
+      </c>
+      <c r="R15" s="10">
         <v>66.59</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>2</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="4">
         <v>44670</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>8.0299999999999994</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <v>22.270575660406166</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>88.584161810078882</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>3.6166110678098211</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <v>0.52041055718475071</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <v>67.89</v>
       </c>
-      <c r="K16" s="11">
-        <v>0</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>0</v>
-      </c>
-      <c r="R16" s="11">
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>0</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>0</v>
+      </c>
+      <c r="R16" s="10">
         <v>67.89</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="4">
         <v>44670</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>7.77</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>4.1170142915019348</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>69.935527655242609</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>1.9285370370370367</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>1.2711864406779663</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <v>1065.9100000000001</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <v>587.61</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <v>55.18</v>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="10">
         <v>54.24</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="10">
         <v>83.01</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="10">
         <v>16.440000000000001</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="10">
         <v>7.41</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="Q17" s="10">
         <v>11.3</v>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="10">
         <v>1881.1000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>2</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="4">
         <v>44670</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>7.77</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>4.3312295642916903</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>71.313202247191015</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>2.2972447097124253</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>1.3487475915221581</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10">
         <v>1049.93</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="10">
         <v>585.02</v>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="10">
         <v>55.21</v>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="10">
         <v>51.17</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="10">
         <v>81.78</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="10">
         <v>7.24</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="10">
         <v>14.29</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="10">
         <v>17.829999999999998</v>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="10">
         <v>1862.47</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="4">
         <v>44670</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>7.66</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>6.0853962654339773</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>77.286356821589223</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>2.7270649966147595</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>1.2363996043521268</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10">
         <v>1388.9</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="10">
         <v>521.11</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="10">
         <v>67.75</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="10">
         <v>46.32</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="10">
         <v>85.69</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="10">
         <v>14.75</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="10">
         <v>13.45</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="10">
         <v>40.590000000000003</v>
       </c>
-      <c r="R19" s="11">
+      <c r="R19" s="10">
         <v>2178.56</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="4">
         <v>44670</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>7.66</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="7">
         <v>6.0112395024310157</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>76.701680672268907</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>2.7082407692307688</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <v>1.2019230769230769</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <v>1334.73</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <v>497.54</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <v>64.790000000000006</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="10">
         <v>44.06</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="10">
         <v>82.04</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="10">
         <v>15.33</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="10">
         <v>9.26</v>
       </c>
-      <c r="Q20" s="11">
+      <c r="Q20" s="10">
         <v>23.62</v>
       </c>
-      <c r="R20" s="11">
+      <c r="R20" s="10">
         <v>2071.37</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>5</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="4">
         <v>44677</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <v>8.17</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="7">
         <v>21.64726175075463</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>93.09428950863213</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>2.99664442700157</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>1.3414762969588552</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <v>60.58</v>
       </c>
-      <c r="K21" s="11">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11">
-        <v>0</v>
-      </c>
-      <c r="P21" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="11">
-        <v>0</v>
-      </c>
-      <c r="R21" s="11">
+      <c r="K21" s="10">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0</v>
+      </c>
+      <c r="R21" s="10">
         <v>60.58</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="A22" s="1">
         <v>5</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="4">
         <v>44677</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6">
         <v>8.19</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="7">
         <v>22.030497592295344</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>92.063492063492049</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>2.777362110311751</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>1.2163854679802955</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <v>59.53</v>
       </c>
-      <c r="K22" s="11">
-        <v>0</v>
-      </c>
-      <c r="L22" s="11">
-        <v>0</v>
-      </c>
-      <c r="M22" s="11">
-        <v>0</v>
-      </c>
-      <c r="N22" s="11">
-        <v>0</v>
-      </c>
-      <c r="O22" s="11">
-        <v>0</v>
-      </c>
-      <c r="P22" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>0</v>
-      </c>
-      <c r="R22" s="11">
+      <c r="K22" s="10">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10">
+        <v>0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0</v>
+      </c>
+      <c r="P22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>0</v>
+      </c>
+      <c r="R22" s="10">
         <v>59.53</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>5</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="4">
         <v>44677</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <v>7.86</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="7">
         <v>3.6486486486486482</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>68.543046357615921</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>2.3259845559845562</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="7">
         <v>1.1472275334608031</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="10">
         <v>1946.99</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <v>826.1</v>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="10">
         <v>215.03</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="10">
         <v>672.93</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="10">
         <v>282.67</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="10">
         <v>174.59</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="10">
         <v>8.0399999999999991</v>
       </c>
-      <c r="Q23" s="11">
+      <c r="Q23" s="10">
         <v>60.23</v>
       </c>
-      <c r="R23" s="11">
+      <c r="R23" s="10">
         <v>4186.58</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="A24" s="1">
         <v>5</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="4">
         <v>44677</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>7.86</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="7">
         <v>3.673897050627549</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>69.127516778523443</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <v>1.813176807444524</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="7">
         <v>1.1307767944936089</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="10">
         <v>1960.01</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="10">
         <v>833.71</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="10">
         <v>217.2</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M24" s="10">
         <v>688.58</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <v>282.11</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="10">
         <v>168.92</v>
       </c>
-      <c r="P24" s="11">
+      <c r="P24" s="10">
         <v>7.62</v>
       </c>
-      <c r="Q24" s="11">
+      <c r="Q24" s="10">
         <v>83.94</v>
       </c>
-      <c r="R24" s="11">
+      <c r="R24" s="10">
         <v>4242.0899999999992</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>5</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="4">
         <v>44677</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <v>7.66</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="7">
         <v>2.3441744935185893</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8">
         <v>77.30949340144744</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>2.1254828815977174</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="7">
         <v>1.0396039603960396</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="10">
         <v>1595.29</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="10">
         <v>680.14</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="10">
         <v>219.52</v>
       </c>
-      <c r="M25" s="11">
+      <c r="M25" s="10">
         <v>526.14</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="10">
         <v>292.22000000000003</v>
       </c>
-      <c r="O25" s="11">
+      <c r="O25" s="10">
         <v>134.18</v>
       </c>
-      <c r="P25" s="11">
+      <c r="P25" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="10">
         <v>85.86</v>
       </c>
-      <c r="R25" s="11">
+      <c r="R25" s="10">
         <v>3541.5499999999993</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="A26" s="1">
         <v>5</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="4">
         <v>44677</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6">
         <v>7.65</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>2.3705144069294684</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8">
         <v>76.94174757281553</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>2.1279524475524476</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="7">
         <v>1.1904761904761905</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="10">
         <v>1599.47</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="10">
         <v>682.77</v>
       </c>
-      <c r="L26" s="11">
+      <c r="L26" s="10">
         <v>221.77</v>
       </c>
-      <c r="M26" s="11">
+      <c r="M26" s="10">
         <v>526.73</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="10">
         <v>293.04000000000002</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="10">
         <v>137.54</v>
       </c>
-      <c r="P26" s="11">
+      <c r="P26" s="10">
         <v>7.84</v>
       </c>
-      <c r="Q26" s="11">
+      <c r="Q26" s="10">
         <v>89.45</v>
       </c>
-      <c r="R26" s="11">
+      <c r="R26" s="10">
         <v>3558.6099999999997</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>3</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="12">
         <v>44818</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="1">
         <v>7.92</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>6.5459439618255235</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>75.021240441801197</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="9">
         <v>3.0426423529411766</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="9">
         <v>1.5120967741935483</v>
       </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="12">
         <v>44818</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="1">
         <v>7.93</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>6.2001910727890577</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>79.403159742539501</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <v>3.1574776119402985</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="9">
         <v>1.5358361774744027</v>
       </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="12">
         <v>44818</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1">
         <v>7.96</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>5.3593939466701883</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>69.623655913978496</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <v>2.6587033831628641</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="9">
         <v>1.0607521697203472</v>
       </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A30">
+      <c r="A30" s="1">
         <v>3</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="12">
         <v>44818</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1">
         <v>7.96</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>5.3483855044158517</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>69.442215088282509</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>2.5681215559157216</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="9">
         <v>1.0692464358452138</v>
       </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="12">
         <v>44818</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="1">
         <v>6.63</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>52.716905187835437</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>88.377518557794275</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <v>12.946277777777777</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="9">
         <v>1.5589873417721518</v>
       </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32">
+      <c r="A32" s="1">
         <v>3</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="12">
         <v>44818</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="1">
         <v>6.56</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>52.810351799433889</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>88.437978560490052</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="9">
         <v>13.620453658536587</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="9">
         <v>1.1015096719932718</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33">
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
         <v>8</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="4">
         <v>44825</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="1">
         <v>8.5</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>6.5232403718459508</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>68.783930510314875</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="9">
         <v>2.44</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="9">
         <v>0.95299999999999996</v>
       </c>
-      <c r="K33" s="21"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34">
+      <c r="J33" s="1"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
         <v>8</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="4">
         <v>44825</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="1">
         <v>8.49</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <v>7.117497531564462</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <v>68.831168831168839</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="9">
         <v>1.9139999999999999</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="9">
         <v>0.63</v>
       </c>
-      <c r="K34" s="21"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A35">
+      <c r="J34" s="1"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
         <v>8</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="4">
         <v>44825</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="1">
         <v>9.2200000000000006</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>17.57367508667657</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>59.952439668839162</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="9">
         <v>1.5229999999999999</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="9">
         <v>0.36499999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A36">
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <v>8</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="4">
         <v>44825</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E36" s="1">
         <v>9.19</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="9">
         <v>19.701901089913701</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <v>55.82006099627246</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="9">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I36" s="10" t="e">
+      <c r="I36" s="9" t="e">
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A37">
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <v>8</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37" s="4">
         <v>44825</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1">
         <v>8.08</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <v>5.9232361736387231</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <v>69.45908460471567</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="9">
         <v>2.0070000000000001</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="9">
         <v>0.70799999999999996</v>
       </c>
-      <c r="K37" s="21"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A38">
+      <c r="J37" s="1"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
         <v>8</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38" s="4">
         <v>44825</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1">
         <v>8.08</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="9">
         <v>6.0716774724926603</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="9">
         <v>69.634782608695645</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="9">
         <v>1.5349999999999999</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="9">
         <v>0.40200000000000002</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A39">
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
         <v>7</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="12">
         <v>44832</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="1">
         <v>8.23</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <v>41.104323089120001</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <v>61.459042432493746</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="9">
         <v>9.0465183486238523</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="9">
         <v>1.1327190542420027</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A40">
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
         <v>7</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="12">
         <v>44832</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E40" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="9">
         <v>38.234347336230478</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="9">
         <v>85.897705746158707</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="9">
         <v>9.503798507462685</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I40" s="9">
         <v>1.5929965928449745</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41">
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
         <v>7</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="12">
         <v>44832</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="1">
         <v>6.88</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="9">
         <v>44.220963172804531</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="9">
         <v>88.244714926329266</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="9">
         <v>9.891721238938052</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I41" s="9">
         <v>1.6887778772951187</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A42">
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
         <v>7</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="12">
         <v>44832</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="1">
         <v>6.88</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="9">
         <v>46.517522592021159</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="9">
         <v>88.178156834873249</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="9">
         <v>8.4997537878787863</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="9">
         <v>1.4416936731907146</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43">
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
         <v>6</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="12">
         <v>44853</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2581,27 +2665,36 @@
       <c r="E43" s="1">
         <v>8.84</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="9">
         <v>29.074306888109579</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="9">
         <v>91.9435593991807</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="9">
         <v>5.6416436915887855</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="9">
         <v>3.313344733242134</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A44">
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
         <v>6</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C44" s="12">
         <v>44853</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2610,27 +2703,36 @@
       <c r="E44" s="1">
         <v>8.83</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="9">
         <v>28.760962446593215</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="9">
         <v>92.14229867083661</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="9">
         <v>5.9723748251748265</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I44" s="9">
         <v>3.6103846153846155</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45">
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
         <v>6</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="12">
         <v>44853</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2639,29 +2741,38 @@
       <c r="E45" s="1">
         <v>7.07</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="9">
         <v>6.3430803835681306</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="9">
         <v>79.60059723777529</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="9">
         <f>2157/1000</f>
         <v>2.157</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I45" s="9">
         <f>958/1000</f>
         <v>0.95799999999999996</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A46">
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
         <v>6</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="12">
         <v>44853</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2670,259 +2781,337 @@
       <c r="E46" s="1">
         <v>7.08</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="9">
         <v>6.1370943683913959</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="9">
         <v>78.881987577639762</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="9">
         <f>1891/1000</f>
         <v>1.891</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="9">
         <f>781/1000</f>
         <v>0.78100000000000003</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A47">
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
         <v>6</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="12">
         <v>44853</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="1">
         <v>7.87</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="9">
         <v>2.0595242902717756</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="9">
         <v>60.000000000000028</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="9">
         <f>1439/1000</f>
         <v>1.4390000000000001</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="9">
         <f>517/1000</f>
         <v>0.51700000000000002</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A48">
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
         <v>6</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="12">
         <v>44853</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="1">
         <v>7.88</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="9">
         <v>2.0702549058353221</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="9">
         <v>59.618208516886952</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="9">
         <f>1581/1000</f>
         <v>1.581</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I48" s="9">
         <f>665/1000</f>
         <v>0.66500000000000004</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A49">
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
         <v>9</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="20">
+      <c r="C49" s="4">
         <v>44859</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="1">
         <v>7.58</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="9">
         <v>2.1114903299203642</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="9">
         <v>57.327586206896562</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="9">
         <v>1.613</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I49" s="9">
         <v>0.66800000000000004</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50">
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
         <v>9</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="20">
+      <c r="C50" s="4">
         <v>44859</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="1">
         <v>7.59</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="9">
         <v>2.1061388913214811</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="9">
         <v>57.311157311157324</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="9">
         <v>1.542</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I50" s="9">
         <v>0.59799999999999998</v>
       </c>
-      <c r="J50" s="21"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51">
+      <c r="J50" s="9"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
         <v>9</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="4">
         <v>44859</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="1">
         <v>7.62</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="9">
         <v>2.6881566925536773</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="9">
         <v>59.638874137015407</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="9">
         <v>1.5640000000000001</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="9">
         <v>0.54300000000000004</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52">
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
         <v>9</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="4">
         <v>44859</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="1">
         <v>7.62</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="9">
         <v>2.6394601285788437</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="9">
         <v>59.657085224407467</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="9">
         <v>1.4630000000000001</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="9">
         <v>0.46100000000000002</v>
       </c>
-      <c r="J52" s="21"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53">
+      <c r="J52" s="9"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
         <v>9</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="4">
         <v>44859</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E53" s="1">
         <v>8.19</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53" s="9">
         <v>5.0737931148462154</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="9">
         <v>61.009771986970705</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="9">
         <v>1.3640000000000001</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="9">
         <v>0.315</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A54">
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
         <v>9</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="4">
         <v>44859</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="1">
         <v>8.19</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54" s="9">
         <v>4.9395866454689985</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="9">
         <v>61.184422272288394</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="9">
         <v>1.4950000000000001</v>
       </c>
-      <c r="I54" s="10">
+      <c r="I54" s="9">
         <v>0.40200000000000002</v>
       </c>
-      <c r="J54" s="21"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2948,4 +3137,10 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{61fd1d36-fecb-47ca-b7d7-d0df0370a198}" enabled="0" method="" siteId="{61fd1d36-fecb-47ca-b7d7-d0df0370a198}" removed="1"/>
+</clbl:labelList>
 </file>